--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -23478,6 +23478,657 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>336</v>
+      </c>
+      <c r="O107" t="n">
+        <v>336</v>
+      </c>
+      <c r="P107" t="n">
+        <v>336</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.09626528126105134</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>336</v>
+      </c>
+      <c r="O108" t="n">
+        <v>336</v>
+      </c>
+      <c r="P108" t="n">
+        <v>336</v>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ108" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB108" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC108" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>755</v>
+      </c>
+      <c r="O109" t="n">
+        <v>755</v>
+      </c>
+      <c r="P109" t="n">
+        <v>755</v>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23511,7 +24162,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -23594,7 +24245,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -23604,7 +24255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -23624,7 +24275,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -23656,7 +24307,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17709</v>
+        <v>18045</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -24129,6 +24129,657 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>348</v>
+      </c>
+      <c r="O110" t="n">
+        <v>348</v>
+      </c>
+      <c r="P110" t="n">
+        <v>348</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.09970332702037461</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>348</v>
+      </c>
+      <c r="O111" t="n">
+        <v>348</v>
+      </c>
+      <c r="P111" t="n">
+        <v>348</v>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>691</v>
+      </c>
+      <c r="O112" t="n">
+        <v>691</v>
+      </c>
+      <c r="P112" t="n">
+        <v>691</v>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24162,7 +24813,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -24245,7 +24896,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -24255,7 +24906,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11">
@@ -24275,7 +24926,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -24307,7 +24958,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18045</v>
+        <v>18393</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24775,6 +24775,657 @@
         </is>
       </c>
       <c r="BC112" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>396</v>
+      </c>
+      <c r="O113" t="n">
+        <v>396</v>
+      </c>
+      <c r="P113" t="n">
+        <v>396</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.1134555100576677</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>396</v>
+      </c>
+      <c r="O114" t="n">
+        <v>396</v>
+      </c>
+      <c r="P114" t="n">
+        <v>396</v>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>787</v>
+      </c>
+      <c r="O115" t="n">
+        <v>787</v>
+      </c>
+      <c r="P115" t="n">
+        <v>787</v>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24813,7 +25464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -24896,7 +25547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -24906,7 +25557,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11">
@@ -24926,7 +25577,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -24958,7 +25609,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18393</v>
+        <v>18789</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -25431,6 +25431,657 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>439</v>
+      </c>
+      <c r="O116" t="n">
+        <v>439</v>
+      </c>
+      <c r="P116" t="n">
+        <v>439</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.125775174028576</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>439</v>
+      </c>
+      <c r="O117" t="n">
+        <v>439</v>
+      </c>
+      <c r="P117" t="n">
+        <v>439</v>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>747</v>
+      </c>
+      <c r="O118" t="n">
+        <v>747</v>
+      </c>
+      <c r="P118" t="n">
+        <v>747</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25464,7 +26115,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -25547,7 +26198,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -25557,7 +26208,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -25577,7 +26228,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
@@ -25609,7 +26260,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18789</v>
+        <v>19228</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -26082,6 +26082,657 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>358</v>
+      </c>
+      <c r="O119" t="n">
+        <v>358</v>
+      </c>
+      <c r="P119" t="n">
+        <v>358</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.102568365153144</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>358</v>
+      </c>
+      <c r="O120" t="n">
+        <v>358</v>
+      </c>
+      <c r="P120" t="n">
+        <v>358</v>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ120" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>817</v>
+      </c>
+      <c r="O121" t="n">
+        <v>817</v>
+      </c>
+      <c r="P121" t="n">
+        <v>817</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26115,7 +26766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -26198,7 +26849,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -26208,7 +26859,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -26228,7 +26879,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
@@ -26260,7 +26911,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19228</v>
+        <v>19586</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -26733,6 +26733,657 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>439</v>
+      </c>
+      <c r="O122" t="n">
+        <v>439</v>
+      </c>
+      <c r="P122" t="n">
+        <v>439</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.125775174028576</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>439</v>
+      </c>
+      <c r="O123" t="n">
+        <v>439</v>
+      </c>
+      <c r="P123" t="n">
+        <v>439</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>746</v>
+      </c>
+      <c r="O124" t="n">
+        <v>746</v>
+      </c>
+      <c r="P124" t="n">
+        <v>746</v>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26766,7 +27417,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -26849,7 +27500,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -26859,7 +27510,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -26879,7 +27530,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -26911,7 +27562,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19586</v>
+        <v>20025</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -765,14 +765,12 @@
       <c r="O2" t="n">
         <v>89</v>
       </c>
+      <c r="P2" t="n">
+        <v>89</v>
+      </c>
       <c r="R2" t="n">
         <v>0.02549883938164753</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -785,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -915,14 +903,12 @@
       <c r="O3" t="n">
         <v>488</v>
       </c>
+      <c r="P3" t="n">
+        <v>488</v>
+      </c>
       <c r="R3" t="n">
         <v>0.139813860879146</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -935,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1065,14 +1041,12 @@
       <c r="O4" t="n">
         <v>529</v>
       </c>
+      <c r="P4" t="n">
+        <v>529</v>
+      </c>
       <c r="R4" t="n">
         <v>0.1515605172235005</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1085,23 +1059,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1215,14 +1179,12 @@
       <c r="O5" t="n">
         <v>515</v>
       </c>
+      <c r="P5" t="n">
+        <v>515</v>
+      </c>
       <c r="R5" t="n">
         <v>0.1475494638376234</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1235,23 +1197,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1365,14 +1317,12 @@
       <c r="O6" t="n">
         <v>487</v>
       </c>
+      <c r="P6" t="n">
+        <v>487</v>
+      </c>
       <c r="R6" t="n">
         <v>0.1395273570658691</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1385,23 +1335,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1515,14 +1455,12 @@
       <c r="O7" t="n">
         <v>643</v>
       </c>
+      <c r="P7" t="n">
+        <v>643</v>
+      </c>
       <c r="R7" t="n">
         <v>0.1842219519370715</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1535,23 +1473,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1665,14 +1593,12 @@
       <c r="O8" t="n">
         <v>549</v>
       </c>
+      <c r="P8" t="n">
+        <v>549</v>
+      </c>
       <c r="R8" t="n">
         <v>0.1572905934890393</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1685,23 +1611,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1815,14 +1731,12 @@
       <c r="O9" t="n">
         <v>570</v>
       </c>
+      <c r="P9" t="n">
+        <v>570</v>
+      </c>
       <c r="R9" t="n">
         <v>0.163307173567855</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1835,23 +1749,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1965,14 +1869,12 @@
       <c r="O10" t="n">
         <v>542</v>
       </c>
+      <c r="P10" t="n">
+        <v>542</v>
+      </c>
       <c r="R10" t="n">
         <v>0.1552850667961007</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1985,23 +1887,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2115,14 +2007,12 @@
       <c r="O11" t="n">
         <v>513</v>
       </c>
+      <c r="P11" t="n">
+        <v>513</v>
+      </c>
       <c r="R11" t="n">
         <v>0.1469764562110694</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2135,23 +2025,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2265,14 +2145,12 @@
       <c r="O12" t="n">
         <v>458</v>
       </c>
+      <c r="P12" t="n">
+        <v>458</v>
+      </c>
       <c r="R12" t="n">
         <v>0.1312187464808379</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2285,23 +2163,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2415,14 +2283,12 @@
       <c r="O13" t="n">
         <v>532</v>
       </c>
+      <c r="P13" t="n">
+        <v>532</v>
+      </c>
       <c r="R13" t="n">
         <v>0.1524200286633313</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2435,23 +2301,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2565,14 +2421,12 @@
       <c r="O14" t="n">
         <v>580</v>
       </c>
+      <c r="P14" t="n">
+        <v>580</v>
+      </c>
       <c r="R14" t="n">
         <v>0.1661722117006244</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2585,23 +2439,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2715,14 +2559,12 @@
       <c r="O15" t="n">
         <v>522</v>
       </c>
+      <c r="P15" t="n">
+        <v>522</v>
+      </c>
       <c r="R15" t="n">
         <v>0.1495549905305619</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2735,23 +2577,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2865,14 +2697,12 @@
       <c r="O16" t="n">
         <v>550</v>
       </c>
+      <c r="P16" t="n">
+        <v>550</v>
+      </c>
       <c r="R16" t="n">
         <v>0.1575770973023162</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2885,23 +2715,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3015,14 +2835,12 @@
       <c r="O17" t="n">
         <v>531</v>
       </c>
+      <c r="P17" t="n">
+        <v>531</v>
+      </c>
       <c r="R17" t="n">
         <v>0.1521335248500544</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3035,23 +2853,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3165,14 +2973,12 @@
       <c r="O18" t="n">
         <v>689</v>
       </c>
+      <c r="P18" t="n">
+        <v>689</v>
+      </c>
       <c r="R18" t="n">
         <v>0.1974011273478107</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3185,23 +2991,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3315,14 +3111,12 @@
       <c r="O19" t="n">
         <v>612</v>
       </c>
+      <c r="P19" t="n">
+        <v>612</v>
+      </c>
       <c r="R19" t="n">
         <v>0.1753403337254864</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3335,23 +3129,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3465,14 +3249,12 @@
       <c r="O20" t="n">
         <v>533</v>
       </c>
+      <c r="P20" t="n">
+        <v>533</v>
+      </c>
       <c r="R20" t="n">
         <v>0.1527065324766082</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3485,23 +3267,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3615,14 +3387,12 @@
       <c r="O21" t="n">
         <v>619</v>
       </c>
+      <c r="P21" t="n">
+        <v>619</v>
+      </c>
       <c r="R21" t="n">
         <v>0.177345860418425</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3635,23 +3405,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3765,14 +3525,12 @@
       <c r="O22" t="n">
         <v>324</v>
       </c>
+      <c r="P22" t="n">
+        <v>324</v>
+      </c>
       <c r="R22" t="n">
         <v>0.09282723550172808</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3785,23 +3543,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3915,14 +3663,12 @@
       <c r="O23" t="n">
         <v>428</v>
       </c>
+      <c r="P23" t="n">
+        <v>428</v>
+      </c>
       <c r="R23" t="n">
         <v>0.1226236320825297</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3935,23 +3681,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4065,14 +3801,12 @@
       <c r="O24" t="n">
         <v>570</v>
       </c>
+      <c r="P24" t="n">
+        <v>570</v>
+      </c>
       <c r="R24" t="n">
         <v>0.163307173567855</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4085,23 +3819,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4215,14 +3939,12 @@
       <c r="O25" t="n">
         <v>541</v>
       </c>
+      <c r="P25" t="n">
+        <v>541</v>
+      </c>
       <c r="R25" t="n">
         <v>0.1549985629828237</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4235,23 +3957,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4365,14 +4077,12 @@
       <c r="O26" t="n">
         <v>469</v>
       </c>
+      <c r="P26" t="n">
+        <v>469</v>
+      </c>
       <c r="R26" t="n">
         <v>0.1343702884268842</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4385,23 +4095,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4515,14 +4215,12 @@
       <c r="O27" t="n">
         <v>507</v>
       </c>
+      <c r="P27" t="n">
+        <v>507</v>
+      </c>
       <c r="R27" t="n">
         <v>0.1452574333314078</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4535,23 +4233,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4665,14 +4353,12 @@
       <c r="O28" t="n">
         <v>434</v>
       </c>
+      <c r="P28" t="n">
+        <v>434</v>
+      </c>
       <c r="R28" t="n">
         <v>0.1243426549621913</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4685,23 +4371,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4815,14 +4491,12 @@
       <c r="O29" t="n">
         <v>400</v>
       </c>
+      <c r="P29" t="n">
+        <v>400</v>
+      </c>
       <c r="R29" t="n">
         <v>0.1146015253107754</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4835,23 +4509,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4965,14 +4629,12 @@
       <c r="O30" t="n">
         <v>545</v>
       </c>
+      <c r="P30" t="n">
+        <v>545</v>
+      </c>
       <c r="R30" t="n">
         <v>0.1561445782359315</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4985,23 +4647,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5115,14 +4767,12 @@
       <c r="O31" t="n">
         <v>489</v>
       </c>
+      <c r="P31" t="n">
+        <v>489</v>
+      </c>
       <c r="R31" t="n">
         <v>0.140100364692423</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5135,23 +4785,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5265,14 +4905,12 @@
       <c r="O32" t="n">
         <v>545</v>
       </c>
+      <c r="P32" t="n">
+        <v>545</v>
+      </c>
       <c r="R32" t="n">
         <v>0.1561445782359315</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5285,23 +4923,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5415,14 +5043,12 @@
       <c r="O33" t="n">
         <v>496</v>
       </c>
+      <c r="P33" t="n">
+        <v>496</v>
+      </c>
       <c r="R33" t="n">
         <v>0.1421058913853615</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5435,23 +5061,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5565,14 +5181,12 @@
       <c r="O34" t="n">
         <v>440</v>
       </c>
+      <c r="P34" t="n">
+        <v>440</v>
+      </c>
       <c r="R34" t="n">
         <v>0.126061677841853</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5585,23 +5199,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5715,14 +5319,12 @@
       <c r="O35" t="n">
         <v>527</v>
       </c>
+      <c r="P35" t="n">
+        <v>527</v>
+      </c>
       <c r="R35" t="n">
         <v>0.1509875095969466</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5735,23 +5337,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5865,14 +5457,12 @@
       <c r="O36" t="n">
         <v>443</v>
       </c>
+      <c r="P36" t="n">
+        <v>443</v>
+      </c>
       <c r="R36" t="n">
         <v>0.1269211892816838</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5885,23 +5475,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6015,14 +5595,12 @@
       <c r="O37" t="n">
         <v>336</v>
       </c>
+      <c r="P37" t="n">
+        <v>336</v>
+      </c>
       <c r="R37" t="n">
         <v>0.09626528126105134</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6035,23 +5613,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6165,14 +5733,12 @@
       <c r="O38" t="n">
         <v>348</v>
       </c>
+      <c r="P38" t="n">
+        <v>348</v>
+      </c>
       <c r="R38" t="n">
         <v>0.09970332702037461</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6185,23 +5751,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6315,14 +5871,12 @@
       <c r="O39" t="n">
         <v>396</v>
       </c>
+      <c r="P39" t="n">
+        <v>396</v>
+      </c>
       <c r="R39" t="n">
         <v>0.1134555100576677</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6335,23 +5889,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6465,14 +6009,12 @@
       <c r="O40" t="n">
         <v>439</v>
       </c>
+      <c r="P40" t="n">
+        <v>439</v>
+      </c>
       <c r="R40" t="n">
         <v>0.125775174028576</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6485,23 +6027,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6615,14 +6147,12 @@
       <c r="O41" t="n">
         <v>358</v>
       </c>
+      <c r="P41" t="n">
+        <v>358</v>
+      </c>
       <c r="R41" t="n">
         <v>0.102568365153144</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6635,23 +6165,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6765,14 +6285,12 @@
       <c r="O42" t="n">
         <v>439</v>
       </c>
+      <c r="P42" t="n">
+        <v>439</v>
+      </c>
       <c r="R42" t="n">
         <v>0.125775174028576</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6785,23 +6303,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6838,6 +6346,144 @@
         </is>
       </c>
       <c r="BC42" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>509</v>
+      </c>
+      <c r="O43" t="n">
+        <v>509</v>
+      </c>
+      <c r="P43" t="n">
+        <v>509</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.1458304409579617</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr"/>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -6876,7 +6522,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6605,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10">
@@ -6969,7 +6615,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -7021,7 +6667,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20025</v>
+        <v>20534</v>
       </c>
     </row>
     <row r="16">
